--- a/PropuestaProyecto/Calendario de actividades.xlsx
+++ b/PropuestaProyecto/Calendario de actividades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elies\Desktop\DECIMO CUATRIMESTRE\INTEGRADORA II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ITZELPROYECTO\integradoraTeampoderoso\PropuestaProyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B9B823E-A018-479C-A233-1359EB0D53F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B749360A-8756-4715-BCE7-25966406223C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30A5C19A-5DFA-4927-AC28-1A5B7C8ACF0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{30A5C19A-5DFA-4927-AC28-1A5B7C8ACF0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t>ACTIVIDADES</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>CAPÍTULO II.  MARCO DE REFERENCIAL</t>
+  </si>
+  <si>
+    <t>INTEGRANTES: REYNA ITZEL DIEGO ESTRADA, ELI ESPINOZA TREVIÑO, LEVI BRAYAN MUNDO ESCAMILLA, ISRRAEL REYES OLMOS</t>
   </si>
 </sst>
 </file>
@@ -244,7 +247,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -385,16 +388,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -405,74 +414,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -486,6 +454,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -498,24 +484,56 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,9 +552,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -574,7 +592,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -680,7 +698,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -822,7 +840,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -833,157 +851,155 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:S90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:S91"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.33203125" customWidth="1"/>
-    <col min="3" max="3" width="42.21875" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="42.28515625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="16.88671875" customWidth="1"/>
-    <col min="7" max="9" width="17.33203125" customWidth="1"/>
-    <col min="10" max="10" width="17.21875" customWidth="1"/>
-    <col min="11" max="11" width="17.5546875" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" customWidth="1"/>
-    <col min="13" max="13" width="17.21875" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" customWidth="1"/>
-    <col min="15" max="15" width="17.44140625" customWidth="1"/>
-    <col min="16" max="16" width="17.21875" customWidth="1"/>
-    <col min="17" max="18" width="17.109375" customWidth="1"/>
+    <col min="5" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" customWidth="1"/>
+    <col min="13" max="14" width="17.28515625" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" customWidth="1"/>
+    <col min="17" max="18" width="17.140625" customWidth="1"/>
     <col min="19" max="19" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B1" s="8">
+    <row r="1" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+    </row>
+    <row r="2" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="48">
         <v>2025</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-    </row>
-    <row r="2" spans="2:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+    </row>
+    <row r="3" spans="2:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7" t="s">
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7" t="s">
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-    </row>
-    <row r="3" spans="2:19" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="4" t="s">
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+    </row>
+    <row r="4" spans="2:19" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S4" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="11" t="s">
+    <row r="5" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="47"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1000,10 +1016,12 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="2:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="27"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="1"/>
+    <row r="6" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1020,13 +1038,11 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="25" t="s">
-        <v>9</v>
-      </c>
+    <row r="7" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="25"/>
       <c r="C7" s="26"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1042,11 +1058,13 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="27"/>
-      <c r="C8" s="28"/>
+    <row r="8" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="24"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1062,14 +1080,12 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="25" t="s">
-        <v>10</v>
-      </c>
+    <row r="9" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="25"/>
       <c r="C9" s="26"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1084,11 +1100,13 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="27"/>
-      <c r="C10" s="28"/>
+    <row r="10" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="24"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1104,14 +1122,12 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="25" t="s">
-        <v>11</v>
-      </c>
+    <row r="11" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="25"/>
       <c r="C11" s="26"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1126,11 +1142,13 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="27"/>
-      <c r="C12" s="28"/>
+    <row r="12" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="24"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1146,14 +1164,12 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
-        <v>12</v>
-      </c>
+    <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="25"/>
       <c r="C13" s="26"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1168,11 +1184,13 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="27"/>
-      <c r="C14" s="28"/>
+    <row r="14" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="24"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="E14" s="12"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1188,14 +1206,12 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="25" t="s">
-        <v>13</v>
-      </c>
+    <row r="15" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="25"/>
       <c r="C15" s="26"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1210,12 +1226,14 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="27"/>
-      <c r="C16" s="28"/>
+    <row r="16" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="24"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="F16" s="12"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1230,14 +1248,12 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="25" t="s">
-        <v>14</v>
-      </c>
+    <row r="17" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="25"/>
       <c r="C17" s="26"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="F17" s="13"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1252,12 +1268,14 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="27"/>
-      <c r="C18" s="28"/>
+    <row r="18" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="24"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="F18" s="12"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1272,15 +1290,13 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
-        <v>15</v>
-      </c>
+    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="25"/>
       <c r="C19" s="26"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1294,9 +1310,11 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="27"/>
-      <c r="C20" s="28"/>
+    <row r="20" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="24"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1314,99 +1332,97 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="16" t="s">
+    <row r="21" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="22" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="13"/>
-    </row>
-    <row r="22" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="14"/>
-    </row>
-    <row r="23" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="25" t="s">
+      <c r="C22" s="40"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="15"/>
+    </row>
+    <row r="23" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="16"/>
+    </row>
+    <row r="24" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-    </row>
-    <row r="24" spans="2:19" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="27"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-    </row>
-    <row r="25" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="25" t="s">
-        <v>22</v>
-      </c>
+      <c r="C24" s="24"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="25"/>
       <c r="C25" s="26"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1420,13 +1436,15 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="27"/>
-      <c r="C26" s="28"/>
+    <row r="26" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="24"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1440,15 +1458,13 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="25" t="s">
-        <v>23</v>
-      </c>
+    <row r="27" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="25"/>
       <c r="C27" s="26"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1462,13 +1478,15 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="27"/>
-      <c r="C28" s="28"/>
+    <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="24"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1482,15 +1500,13 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="2:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="22"/>
+    <row r="29" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="25"/>
+      <c r="C29" s="26"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1504,13 +1520,15 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="23"/>
-      <c r="C30" s="24"/>
+    <row r="30" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="36"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1524,15 +1542,13 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="22"/>
+    <row r="31" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="37"/>
+      <c r="C31" s="38"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -1546,13 +1562,15 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
+    <row r="32" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="36"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -1566,75 +1584,73 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="2:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="11" t="s">
+    <row r="33" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="37"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+    </row>
+    <row r="34" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="13"/>
-      <c r="S33" s="12"/>
-    </row>
-    <row r="34" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="12"/>
-    </row>
-    <row r="35" spans="2:19" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="11" t="s">
+      <c r="C34" s="40"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="41"/>
+    </row>
+    <row r="35" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="41"/>
+    </row>
+    <row r="36" spans="2:19" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-    </row>
-    <row r="36" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="26"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -1652,13 +1668,15 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="27"/>
-      <c r="C37" s="28"/>
+    <row r="37" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="24"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="G37" s="12"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -1672,205 +1690,203 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="41" t="s">
+    <row r="38" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+    </row>
+    <row r="39" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
-      <c r="N38" s="32"/>
-      <c r="O38" s="32"/>
-      <c r="P38" s="32"/>
-      <c r="Q38" s="32"/>
-      <c r="R38" s="32"/>
-      <c r="S38" s="32"/>
-    </row>
-    <row r="39" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="37" t="s">
+      <c r="C39" s="28"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+    </row>
+    <row r="40" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="38"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="32"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="32"/>
-      <c r="R39" s="32"/>
-      <c r="S39" s="32"/>
-    </row>
-    <row r="40" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="39"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
-      <c r="N40" s="32"/>
-      <c r="O40" s="32"/>
-      <c r="P40" s="32"/>
-      <c r="Q40" s="32"/>
-      <c r="R40" s="32"/>
-      <c r="S40" s="32"/>
-    </row>
-    <row r="41" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="37" t="s">
+      <c r="C40" s="30"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+    </row>
+    <row r="41" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="31"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+    </row>
+    <row r="42" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="38"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="32"/>
-      <c r="O41" s="32"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="32"/>
-      <c r="R41" s="32"/>
-      <c r="S41" s="32"/>
-    </row>
-    <row r="42" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="39"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
-      <c r="N42" s="32"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="32"/>
-      <c r="R42" s="32"/>
-      <c r="S42" s="32"/>
-    </row>
-    <row r="43" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="37" t="s">
+      <c r="C42" s="30"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+    </row>
+    <row r="43" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="31"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
+    </row>
+    <row r="44" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="38"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="32"/>
-      <c r="R43" s="32"/>
-      <c r="S43" s="32"/>
-    </row>
-    <row r="44" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="39"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
-      <c r="M44" s="32"/>
-      <c r="N44" s="32"/>
-      <c r="O44" s="32"/>
-      <c r="P44" s="32"/>
-      <c r="Q44" s="32"/>
-      <c r="R44" s="32"/>
-      <c r="S44" s="32"/>
-    </row>
-    <row r="45" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="25" t="s">
+      <c r="C44" s="30"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+    </row>
+    <row r="45" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="31"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+    </row>
+    <row r="46" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
-      <c r="N45" s="32"/>
-      <c r="O45" s="32"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="32"/>
-      <c r="R45" s="32"/>
-      <c r="S45" s="32"/>
-    </row>
-    <row r="46" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="27"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-    </row>
-    <row r="47" spans="2:19" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="C46" s="24"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+    </row>
+    <row r="47" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="25"/>
       <c r="C47" s="26"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+      <c r="G47" s="13"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -1884,15 +1900,16 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="27"/>
-      <c r="C48" s="28"/>
+    <row r="48" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="24"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="H48" s="12"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -1904,16 +1921,14 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="25" t="s">
-        <v>28</v>
-      </c>
+    <row r="49" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="25"/>
       <c r="C49" s="26"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+      <c r="H49" s="13"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -1926,17 +1941,19 @@
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
     </row>
-    <row r="50" spans="2:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="27"/>
-      <c r="C50" s="28"/>
+    <row r="50" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="24"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
@@ -1946,265 +1963,263 @@
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="17" t="s">
+    <row r="51" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="25"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+    </row>
+    <row r="52" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="18"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
-      <c r="M51" s="32"/>
-      <c r="N51" s="32"/>
-      <c r="O51" s="32"/>
-      <c r="P51" s="32"/>
-      <c r="Q51" s="32"/>
-      <c r="R51" s="32"/>
-      <c r="S51" s="32"/>
-    </row>
-    <row r="52" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="25" t="s">
+      <c r="C52" s="18"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11"/>
+      <c r="S52" s="11"/>
+    </row>
+    <row r="53" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C52" s="26"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
-      <c r="M52" s="32"/>
-      <c r="N52" s="32"/>
-      <c r="O52" s="32"/>
-      <c r="P52" s="32"/>
-      <c r="Q52" s="32"/>
-      <c r="R52" s="32"/>
-      <c r="S52" s="32"/>
-    </row>
-    <row r="53" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="27"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
-      <c r="L53" s="32"/>
-      <c r="M53" s="32"/>
-      <c r="N53" s="32"/>
-      <c r="O53" s="32"/>
-      <c r="P53" s="32"/>
-      <c r="Q53" s="32"/>
-      <c r="R53" s="32"/>
-      <c r="S53" s="32"/>
-    </row>
-    <row r="54" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="25" t="s">
+      <c r="C53" s="24"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+    </row>
+    <row r="54" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="25"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
+    </row>
+    <row r="55" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="26"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
-      <c r="M54" s="32"/>
-      <c r="N54" s="32"/>
-      <c r="O54" s="32"/>
-      <c r="P54" s="32"/>
-      <c r="Q54" s="32"/>
-      <c r="R54" s="32"/>
-      <c r="S54" s="32"/>
-    </row>
-    <row r="55" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="27"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
-      <c r="M55" s="32"/>
-      <c r="N55" s="32"/>
-      <c r="O55" s="32"/>
-      <c r="P55" s="32"/>
-      <c r="Q55" s="32"/>
-      <c r="R55" s="32"/>
-      <c r="S55" s="32"/>
-    </row>
-    <row r="56" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="17" t="s">
+      <c r="C55" s="24"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11"/>
+      <c r="S55" s="11"/>
+    </row>
+    <row r="56" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="25"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11"/>
+      <c r="S56" s="11"/>
+    </row>
+    <row r="57" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="18"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32"/>
-      <c r="L56" s="32"/>
-      <c r="M56" s="32"/>
-      <c r="N56" s="32"/>
-      <c r="O56" s="32"/>
-      <c r="P56" s="32"/>
-      <c r="Q56" s="32"/>
-      <c r="R56" s="29"/>
-      <c r="S56" s="32"/>
-    </row>
-    <row r="57" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="33" t="s">
+      <c r="C57" s="18"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+      <c r="R57" s="8"/>
+      <c r="S57" s="11"/>
+    </row>
+    <row r="58" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C57" s="34"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
-      <c r="N57" s="32"/>
-      <c r="O57" s="32"/>
-      <c r="P57" s="32"/>
-      <c r="Q57" s="32"/>
-      <c r="R57" s="30"/>
-      <c r="S57" s="32"/>
-    </row>
-    <row r="58" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="35"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
-      <c r="M58" s="32"/>
-      <c r="N58" s="32"/>
-      <c r="O58" s="32"/>
-      <c r="P58" s="32"/>
-      <c r="Q58" s="32"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="32"/>
-    </row>
-    <row r="59" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="25" t="s">
+      <c r="C58" s="20"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="11"/>
+      <c r="O58" s="11"/>
+      <c r="P58" s="11"/>
+      <c r="Q58" s="11"/>
+      <c r="R58" s="9"/>
+      <c r="S58" s="11"/>
+    </row>
+    <row r="59" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="21"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
+      <c r="R59" s="9"/>
+      <c r="S59" s="11"/>
+    </row>
+    <row r="60" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="26"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
-      <c r="M59" s="32"/>
-      <c r="N59" s="32"/>
-      <c r="O59" s="32"/>
-      <c r="P59" s="32"/>
-      <c r="Q59" s="32"/>
-      <c r="R59" s="30"/>
-      <c r="S59" s="32"/>
-    </row>
-    <row r="60" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="27"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
-      <c r="M60" s="32"/>
-      <c r="N60" s="32"/>
-      <c r="O60" s="32"/>
-      <c r="P60" s="32"/>
-      <c r="Q60" s="32"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="32"/>
-    </row>
-    <row r="61" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="33" t="s">
+      <c r="C60" s="24"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="9"/>
+      <c r="S60" s="11"/>
+    </row>
+    <row r="61" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="25"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="11"/>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="11"/>
+    </row>
+    <row r="62" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C61" s="34"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32"/>
-      <c r="L61" s="32"/>
-      <c r="M61" s="32"/>
-      <c r="N61" s="32"/>
-      <c r="O61" s="32"/>
-      <c r="P61" s="32"/>
-      <c r="Q61" s="32"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="32"/>
-    </row>
-    <row r="62" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="35"/>
-      <c r="C62" s="36"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-    </row>
-    <row r="63" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="34"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="11"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="11"/>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="11"/>
+    </row>
+    <row r="63" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="21"/>
+      <c r="C63" s="22"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -2222,16 +2237,18 @@
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
     </row>
-    <row r="64" spans="2:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="35"/>
-      <c r="C64" s="36"/>
+    <row r="64" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="20"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+      <c r="J64" s="12"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -2242,11 +2259,9 @@
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
     </row>
-    <row r="65" spans="2:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="26"/>
+    <row r="65" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="21"/>
+      <c r="C65" s="22"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -2264,18 +2279,20 @@
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
     </row>
-    <row r="66" spans="2:19" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="27"/>
-      <c r="C66" s="28"/>
+    <row r="66" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="24"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="1"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
@@ -2284,134 +2301,131 @@
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
     </row>
-    <row r="67" spans="2:19" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="15" t="s">
+    <row r="67" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="25"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+    </row>
+    <row r="68" spans="2:19" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
-      <c r="L67" s="13"/>
-      <c r="M67" s="13"/>
-      <c r="N67" s="13"/>
-      <c r="O67" s="13"/>
-      <c r="P67" s="13"/>
-      <c r="Q67" s="13"/>
-      <c r="R67" s="13"/>
-      <c r="S67" s="13"/>
-    </row>
-    <row r="68" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-      <c r="N68" s="14"/>
-      <c r="O68" s="14"/>
-      <c r="P68" s="14"/>
-      <c r="Q68" s="14"/>
-      <c r="R68" s="14"/>
-      <c r="S68" s="14"/>
-    </row>
-    <row r="69" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
-      <c r="P69" s="13"/>
-      <c r="Q69" s="13"/>
-      <c r="R69" s="13"/>
-      <c r="S69" s="13"/>
-    </row>
-    <row r="70" spans="2:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
-      <c r="O70" s="14"/>
-      <c r="P70" s="14"/>
-      <c r="Q70" s="14"/>
-      <c r="R70" s="14"/>
-      <c r="S70" s="14"/>
-    </row>
-    <row r="71" spans="2:19" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="25" t="s">
+      <c r="C68" s="45"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="15"/>
+      <c r="Q68" s="15"/>
+      <c r="R68" s="15"/>
+      <c r="S68" s="15"/>
+    </row>
+    <row r="69" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="45"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16"/>
+      <c r="S69" s="16"/>
+    </row>
+    <row r="70" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="45"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="15"/>
+      <c r="S70" s="15"/>
+    </row>
+    <row r="71" spans="2:19" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="45"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+      <c r="O71" s="16"/>
+      <c r="P71" s="16"/>
+      <c r="Q71" s="16"/>
+      <c r="R71" s="16"/>
+      <c r="S71" s="16"/>
+    </row>
+    <row r="72" spans="2:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C71" s="26"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
-      <c r="M71" s="32"/>
-      <c r="N71" s="32"/>
-      <c r="O71" s="32"/>
-      <c r="P71" s="32"/>
-      <c r="Q71" s="32"/>
-      <c r="R71" s="32"/>
-      <c r="S71" s="32"/>
-    </row>
-    <row r="72" spans="2:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="27"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
-    </row>
-    <row r="73" spans="2:19" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="25" t="s">
-        <v>34</v>
-      </c>
+      <c r="C72" s="24"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="12"/>
+      <c r="N72" s="12"/>
+      <c r="O72" s="12"/>
+      <c r="Q72" s="11"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="11"/>
+    </row>
+    <row r="73" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="25"/>
       <c r="C73" s="26"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -2430,9 +2444,11 @@
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="27"/>
-      <c r="C74" s="28"/>
+    <row r="74" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" s="24"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -2443,17 +2459,13 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
+      <c r="N74" s="12"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="25" t="s">
-        <v>35</v>
-      </c>
+    <row r="75" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="25"/>
       <c r="C75" s="26"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -2467,14 +2479,16 @@
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
+      <c r="P75" s="11"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" spans="2:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="27"/>
-      <c r="C76" s="28"/>
+    <row r="76" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" s="24"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
@@ -2486,16 +2500,14 @@
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="11"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" spans="2:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="25" t="s">
-        <v>36</v>
-      </c>
+    <row r="77" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="25"/>
       <c r="C77" s="26"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -2514,9 +2526,11 @@
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="27"/>
-      <c r="C78" s="28"/>
+    <row r="78" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C78" s="24"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
@@ -2529,15 +2543,13 @@
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
-      <c r="P78" s="1"/>
-      <c r="Q78" s="1"/>
+      <c r="P78" s="12"/>
+      <c r="Q78" s="11"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
     </row>
-    <row r="79" spans="2:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="25" t="s">
-        <v>37</v>
-      </c>
+    <row r="79" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="25"/>
       <c r="C79" s="26"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -2556,9 +2568,11 @@
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
     </row>
-    <row r="80" spans="2:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="27"/>
-      <c r="C80" s="28"/>
+    <row r="80" spans="2:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C80" s="24"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -2571,16 +2585,14 @@
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
-      <c r="P80" s="1"/>
+      <c r="P80" s="12"/>
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
     </row>
-    <row r="81" spans="2:19" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C81" s="10"/>
+    <row r="81" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="25"/>
+      <c r="C81" s="26"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -2598,11 +2610,11 @@
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="26"/>
+    <row r="82" spans="2:19" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C82" s="45"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -2620,9 +2632,11 @@
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
     </row>
-    <row r="83" spans="2:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="27"/>
-      <c r="C83" s="28"/>
+    <row r="83" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="24"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -2635,15 +2649,13 @@
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
-      <c r="P83" s="1"/>
+      <c r="P83" s="12"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
     </row>
-    <row r="84" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="25" t="s">
-        <v>40</v>
-      </c>
+    <row r="84" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="25"/>
       <c r="C84" s="26"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -2662,9 +2674,11 @@
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
     </row>
-    <row r="85" spans="2:19" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="27"/>
-      <c r="C85" s="28"/>
+    <row r="85" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" s="24"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -2677,15 +2691,13 @@
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
-      <c r="P85" s="1"/>
+      <c r="P85" s="12"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="25" t="s">
-        <v>6</v>
-      </c>
+    <row r="86" spans="2:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="25"/>
       <c r="C86" s="26"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -2704,9 +2716,11 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
     </row>
-    <row r="87" spans="2:19" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="27"/>
-      <c r="C87" s="28"/>
+    <row r="87" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="24"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -2719,196 +2733,215 @@
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
-      <c r="P87" s="1"/>
+      <c r="P87" s="12"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
-      <c r="S87" s="1"/>
-    </row>
-    <row r="88" spans="2:19" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3"/>
-      <c r="O88" s="3"/>
-      <c r="P88" s="3"/>
-      <c r="Q88" s="3"/>
-      <c r="R88" s="3"/>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="2:19" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="43" t="s">
+      <c r="S87" s="11"/>
+    </row>
+    <row r="88" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="25"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
+    </row>
+    <row r="89" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="2"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="2"/>
+    </row>
+    <row r="90" spans="2:19" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="G89" s="44"/>
-      <c r="H89" s="45"/>
-      <c r="I89" s="45"/>
-      <c r="J89" s="19"/>
-      <c r="K89" s="19"/>
-      <c r="L89" s="19"/>
-      <c r="M89" s="20"/>
-      <c r="N89" s="3"/>
-      <c r="O89" s="3"/>
-      <c r="P89" s="3"/>
-      <c r="Q89" s="3"/>
-      <c r="R89" s="3"/>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="2:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="43" t="s">
+      <c r="G90" s="34"/>
+      <c r="H90" s="42"/>
+      <c r="I90" s="42"/>
+      <c r="J90" s="44"/>
+      <c r="K90" s="44"/>
+      <c r="L90" s="44"/>
+      <c r="M90" s="7"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="2"/>
+    </row>
+    <row r="91" spans="2:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="G90" s="44"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="19"/>
-      <c r="K90" s="19"/>
-      <c r="L90" s="19"/>
-      <c r="M90" s="20"/>
-      <c r="N90" s="3"/>
-      <c r="O90" s="3"/>
-      <c r="P90" s="3"/>
-      <c r="Q90" s="3"/>
-      <c r="R90" s="3"/>
-      <c r="S90" s="3"/>
+      <c r="G91" s="34"/>
+      <c r="H91" s="43"/>
+      <c r="I91" s="43"/>
+      <c r="J91" s="44"/>
+      <c r="K91" s="44"/>
+      <c r="L91" s="44"/>
+      <c r="M91" s="7"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="119">
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="B41:C42"/>
-    <mergeCell ref="B43:C44"/>
-    <mergeCell ref="F89:G89"/>
+  <mergeCells count="118">
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="B2:S2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B68:C71"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="B62:C63"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="B66:C67"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="Q68:Q69"/>
+    <mergeCell ref="Q70:Q71"/>
+    <mergeCell ref="L68:L69"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="N70:N71"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="S34:S35"/>
+    <mergeCell ref="Q34:Q35"/>
+    <mergeCell ref="P34:P35"/>
+    <mergeCell ref="O34:O35"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="R34:R35"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
     <mergeCell ref="F90:G90"/>
-    <mergeCell ref="R67:R68"/>
-    <mergeCell ref="R69:R70"/>
-    <mergeCell ref="S67:S68"/>
-    <mergeCell ref="S69:S70"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C58"/>
-    <mergeCell ref="B59:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C53"/>
-    <mergeCell ref="B54:C55"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="J67:J68"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K67:K68"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L67:L68"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="M67:M68"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="N67:N68"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O67:O68"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P67:P68"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="Q67:Q68"/>
-    <mergeCell ref="Q69:Q70"/>
-    <mergeCell ref="B77:C78"/>
-    <mergeCell ref="B79:C80"/>
-    <mergeCell ref="B82:C83"/>
-    <mergeCell ref="B84:C85"/>
-    <mergeCell ref="B86:C87"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="B19:C20"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="R33:R34"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="B45:C46"/>
-    <mergeCell ref="B47:C48"/>
-    <mergeCell ref="B49:C50"/>
-    <mergeCell ref="B61:C62"/>
-    <mergeCell ref="B63:C64"/>
-    <mergeCell ref="B65:C66"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="B71:C72"/>
-    <mergeCell ref="B73:C74"/>
-    <mergeCell ref="B75:C76"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="S21:S22"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="B21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B67:C70"/>
-    <mergeCell ref="M33:M34"/>
-    <mergeCell ref="L33:L34"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="S33:S34"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="P33:P34"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="N33:N34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="B78:C79"/>
+    <mergeCell ref="B80:C81"/>
+    <mergeCell ref="B83:C84"/>
+    <mergeCell ref="B85:C86"/>
+    <mergeCell ref="B87:C88"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="B72:C73"/>
+    <mergeCell ref="B74:C75"/>
+    <mergeCell ref="B76:C77"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="E70:E71"/>
     <mergeCell ref="B1:S1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B9:C10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="B13:C14"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="R68:R69"/>
+    <mergeCell ref="R70:R71"/>
+    <mergeCell ref="S68:S69"/>
+    <mergeCell ref="S70:S71"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C59"/>
+    <mergeCell ref="B60:C61"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C54"/>
+    <mergeCell ref="B55:C56"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="K70:K71"/>
+    <mergeCell ref="O70:O71"/>
+    <mergeCell ref="P68:P69"/>
+    <mergeCell ref="P70:P71"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="34" orientation="landscape" r:id="rId1"/>

--- a/PropuestaProyecto/Calendario de actividades.xlsx
+++ b/PropuestaProyecto/Calendario de actividades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ITZELPROYECTO\integradoraTeampoderoso\PropuestaProyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elies\Documents\GitHub\integradoraTeampoderoso\PropuestaProyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B749360A-8756-4715-BCE7-25966406223C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F155780-D1A5-442A-BBAA-31B1D10B2E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{30A5C19A-5DFA-4927-AC28-1A5B7C8ACF0F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30A5C19A-5DFA-4927-AC28-1A5B7C8ACF0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>ACTIVIDADES</t>
   </si>
@@ -46,12 +46,6 @@
   </si>
   <si>
     <t>Semana 4</t>
-  </si>
-  <si>
-    <t>5.3 ANEXOS</t>
-  </si>
-  <si>
-    <t>5.1  CONCLUSIONES</t>
   </si>
   <si>
     <t>1.1 ESTADO DEL ARTE</t>
@@ -151,9 +145,6 @@
   </si>
   <si>
     <t>CAPÍTULO V RESULTADOS</t>
-  </si>
-  <si>
-    <t>5.2 REFERENCIAS BIBLIOGRÁFICAS</t>
   </si>
   <si>
     <t>CAPÍTULO I MARCO CONCEPTUAL</t>
@@ -247,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -323,17 +314,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -401,16 +381,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -418,16 +395,44 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -436,41 +441,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -480,15 +458,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -498,9 +476,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -510,6 +485,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -531,8 +512,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,9 +545,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -592,7 +585,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -698,7 +691,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -840,7 +833,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -851,100 +844,93 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:S91"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:Q86"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33.28515625" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="42.33203125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" customWidth="1"/>
-    <col min="13" max="14" width="17.28515625" customWidth="1"/>
-    <col min="15" max="15" width="17.42578125" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" customWidth="1"/>
-    <col min="17" max="18" width="17.140625" customWidth="1"/>
-    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="5" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="10" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="17.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" customWidth="1"/>
+    <col min="13" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="17.44140625" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" customWidth="1"/>
+    <col min="17" max="17" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B1" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-    </row>
-    <row r="2" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="48">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+    </row>
+    <row r="2" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="47">
         <v>2025</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-    </row>
-    <row r="3" spans="2:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="47" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+    </row>
+    <row r="3" spans="2:17" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47" t="s">
+      <c r="C3" s="46"/>
+      <c r="D3" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47" t="s">
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-    </row>
-    <row r="4" spans="2:19" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
+      <c r="Q3" s="46"/>
+    </row>
+    <row r="4" spans="2:17" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
@@ -987,18 +973,12 @@
       <c r="Q4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="40"/>
+    </row>
+    <row r="5" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="37"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1013,15 +993,13 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="12"/>
+    </row>
+    <row r="6" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1035,14 +1013,12 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+    </row>
+    <row r="7" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1055,16 +1031,14 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="24"/>
+    </row>
+    <row r="8" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="19"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="12"/>
+      <c r="E8" s="9"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1077,15 +1051,13 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
+    </row>
+    <row r="9" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1097,16 +1069,14 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-    </row>
-    <row r="10" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="24"/>
+    </row>
+    <row r="10" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="19"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="12"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1119,15 +1089,13 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-    </row>
-    <row r="11" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
+    </row>
+    <row r="11" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="20"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1139,16 +1107,14 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-    </row>
-    <row r="12" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="24"/>
+    </row>
+    <row r="12" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="19"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="12"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1161,15 +1127,13 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-    </row>
-    <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
+    </row>
+    <row r="13" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1181,16 +1145,14 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="24"/>
+    </row>
+    <row r="14" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="19"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="12"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1203,15 +1165,13 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-    </row>
-    <row r="15" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
+    </row>
+    <row r="15" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="20"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1223,17 +1183,15 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="24"/>
+    </row>
+    <row r="16" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="19"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1245,15 +1203,13 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-    </row>
-    <row r="17" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
+    </row>
+    <row r="17" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="13"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1265,17 +1221,15 @@
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-    </row>
-    <row r="18" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="24"/>
+    </row>
+    <row r="18" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="19"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1287,16 +1241,14 @@
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-    </row>
-    <row r="19" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
+    </row>
+    <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1307,14 +1259,12 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-    </row>
-    <row r="20" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="24"/>
+    </row>
+    <row r="20" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="19"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1329,12 +1279,10 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-    </row>
-    <row r="21" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
+    </row>
+    <row r="21" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1349,80 +1297,72 @@
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-    </row>
-    <row r="22" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="15"/>
-    </row>
-    <row r="23" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="16"/>
-    </row>
-    <row r="24" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-    </row>
-    <row r="25" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
+    </row>
+    <row r="22" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+    </row>
+    <row r="23" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+    </row>
+    <row r="24" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+    </row>
+    <row r="25" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="6"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="5"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1433,18 +1373,16 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-    </row>
-    <row r="26" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="24"/>
+    </row>
+    <row r="26" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="19"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="6"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="5"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1455,16 +1393,14 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-    </row>
-    <row r="27" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="25"/>
-      <c r="C27" s="26"/>
+    </row>
+    <row r="27" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="6"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="5"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1475,18 +1411,16 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-    </row>
-    <row r="28" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="24"/>
+    </row>
+    <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="19"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="6"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="5"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1497,16 +1431,14 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-    </row>
-    <row r="29" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="25"/>
-      <c r="C29" s="26"/>
+    </row>
+    <row r="29" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="6"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="5"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1517,18 +1449,16 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-    </row>
-    <row r="30" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="36"/>
+    </row>
+    <row r="30" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="33"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="6"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1539,16 +1469,14 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-    </row>
-    <row r="31" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="37"/>
-      <c r="C31" s="38"/>
+    </row>
+    <row r="31" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="34"/>
+      <c r="C31" s="35"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="6"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -1559,18 +1487,16 @@
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-    </row>
-    <row r="32" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="36"/>
+    </row>
+    <row r="32" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="33"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="6"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="5"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -1581,16 +1507,14 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-    </row>
-    <row r="33" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="37"/>
-      <c r="C33" s="38"/>
+    </row>
+    <row r="33" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="34"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="6"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="5"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -1601,56 +1525,50 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-    </row>
-    <row r="34" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="41"/>
-    </row>
-    <row r="35" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="41"/>
-    </row>
-    <row r="36" spans="2:19" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="40"/>
+    </row>
+    <row r="34" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+    </row>
+    <row r="35" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+    </row>
+    <row r="36" spans="2:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="37"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -1665,18 +1583,16 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-    </row>
-    <row r="37" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="24"/>
+    </row>
+    <row r="37" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="19"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="9"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -1687,206 +1603,186 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-    </row>
-    <row r="38" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
+    </row>
+    <row r="38" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-    </row>
-    <row r="39" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="27" t="s">
+    </row>
+    <row r="39" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
+    </row>
+    <row r="40" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="27"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="8"/>
+    </row>
+    <row r="41" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
+    </row>
+    <row r="42" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="27"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+      <c r="Q42" s="8"/>
+    </row>
+    <row r="43" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+      <c r="Q43" s="8"/>
+    </row>
+    <row r="44" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11"/>
-      <c r="R39" s="11"/>
-      <c r="S39" s="11"/>
-    </row>
-    <row r="40" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
-      <c r="S40" s="11"/>
-    </row>
-    <row r="41" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="31"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="11"/>
-      <c r="S41" s="11"/>
-    </row>
-    <row r="42" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="11"/>
-    </row>
-    <row r="43" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="31"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="11"/>
-    </row>
-    <row r="44" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="11"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="11"/>
-    </row>
-    <row r="45" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="31"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-    </row>
-    <row r="46" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="23" t="s">
+      <c r="C44" s="27"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+      <c r="Q44" s="8"/>
+    </row>
+    <row r="45" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="28"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
+      <c r="Q45" s="8"/>
+    </row>
+    <row r="46" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="24"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
-    </row>
-    <row r="47" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8"/>
+    </row>
+    <row r="47" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="13"/>
+      <c r="G47" s="10"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -1897,19 +1793,17 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-    </row>
-    <row r="48" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C48" s="24"/>
+    </row>
+    <row r="48" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="19"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="12"/>
+      <c r="H48" s="9"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -1918,17 +1812,15 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-    </row>
-    <row r="49" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="25"/>
-      <c r="C49" s="26"/>
+    </row>
+    <row r="49" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="20"/>
+      <c r="C49" s="21"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="13"/>
+      <c r="H49" s="10"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -1938,34 +1830,30 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-    </row>
-    <row r="50" spans="2:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="24"/>
+    </row>
+    <row r="50" spans="2:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="19"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-    </row>
-    <row r="51" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="25"/>
-      <c r="C51" s="26"/>
+    </row>
+    <row r="51" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -1980,246 +1868,222 @@
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="1"/>
-    </row>
-    <row r="52" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C52" s="18"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
-      <c r="R52" s="11"/>
-      <c r="S52" s="11"/>
-    </row>
-    <row r="53" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="24"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="11"/>
-      <c r="Q53" s="11"/>
-      <c r="R53" s="11"/>
-      <c r="S53" s="11"/>
-    </row>
-    <row r="54" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="25"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
+    </row>
+    <row r="52" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+    </row>
+    <row r="53" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="19"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
+      <c r="Q53" s="8"/>
+    </row>
+    <row r="54" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="20"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="11"/>
-      <c r="Q54" s="11"/>
-      <c r="R54" s="11"/>
-      <c r="S54" s="11"/>
-    </row>
-    <row r="55" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C55" s="24"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="11"/>
-      <c r="P55" s="11"/>
-      <c r="Q55" s="11"/>
-      <c r="R55" s="11"/>
-      <c r="S55" s="11"/>
-    </row>
-    <row r="56" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="25"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="8"/>
+    </row>
+    <row r="55" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="8"/>
+    </row>
+    <row r="56" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="20"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
-      <c r="Q56" s="11"/>
-      <c r="R56" s="11"/>
-      <c r="S56" s="11"/>
-    </row>
-    <row r="57" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C57" s="18"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="11"/>
-      <c r="Q57" s="11"/>
-      <c r="R57" s="8"/>
-      <c r="S57" s="11"/>
-    </row>
-    <row r="58" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" s="20"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="11"/>
-      <c r="P58" s="11"/>
-      <c r="Q58" s="11"/>
-      <c r="R58" s="9"/>
-      <c r="S58" s="11"/>
-    </row>
-    <row r="59" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="21"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+    </row>
+    <row r="57" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="13"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="8"/>
+    </row>
+    <row r="58" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="15"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
+      <c r="Q58" s="8"/>
+    </row>
+    <row r="59" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="16"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
       <c r="K59" s="1"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="11"/>
-      <c r="Q59" s="11"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="11"/>
-    </row>
-    <row r="60" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C60" s="24"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="12"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="11"/>
-      <c r="P60" s="11"/>
-      <c r="Q60" s="11"/>
-      <c r="R60" s="9"/>
-      <c r="S60" s="11"/>
-    </row>
-    <row r="61" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="25"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
+      <c r="Q59" s="8"/>
+    </row>
+    <row r="60" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
+      <c r="Q60" s="8"/>
+    </row>
+    <row r="61" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="20"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="11"/>
-      <c r="Q61" s="11"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="11"/>
-    </row>
-    <row r="62" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C62" s="20"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="12"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="11"/>
-      <c r="Q62" s="11"/>
-      <c r="R62" s="10"/>
-      <c r="S62" s="11"/>
-    </row>
-    <row r="63" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="21"/>
-      <c r="C63" s="22"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
+      <c r="Q61" s="8"/>
+    </row>
+    <row r="62" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="15"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="8"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="8"/>
+    </row>
+    <row r="63" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="16"/>
+      <c r="C63" s="17"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -2234,21 +2098,19 @@
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="1"/>
-    </row>
-    <row r="64" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C64" s="20"/>
+    </row>
+    <row r="64" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" s="15"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="J64" s="12"/>
+      <c r="J64" s="9"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -2256,12 +2118,10 @@
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-    </row>
-    <row r="65" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="21"/>
-      <c r="C65" s="22"/>
+    </row>
+    <row r="65" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="16"/>
+      <c r="C65" s="17"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -2276,34 +2136,30 @@
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-      <c r="S65" s="1"/>
-    </row>
-    <row r="66" spans="2:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="24"/>
+    </row>
+    <row r="66" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="19"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12"/>
-      <c r="L66" s="12"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
-      <c r="R66" s="1"/>
-      <c r="S66" s="1"/>
-    </row>
-    <row r="67" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="25"/>
-      <c r="C67" s="26"/>
+    </row>
+    <row r="67" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="20"/>
+      <c r="C67" s="21"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -2318,115 +2174,103 @@
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-    </row>
-    <row r="68" spans="2:19" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" s="45"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12"/>
-      <c r="O68" s="11"/>
-      <c r="P68" s="15"/>
-      <c r="Q68" s="15"/>
-      <c r="R68" s="15"/>
-      <c r="S68" s="15"/>
-    </row>
-    <row r="69" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="16"/>
-      <c r="R69" s="16"/>
-      <c r="S69" s="16"/>
-    </row>
-    <row r="70" spans="2:19" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="15"/>
-      <c r="O70" s="15"/>
-      <c r="P70" s="15"/>
-      <c r="Q70" s="15"/>
-      <c r="R70" s="15"/>
-      <c r="S70" s="15"/>
-    </row>
-    <row r="71" spans="2:19" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="16"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="16"/>
-      <c r="O71" s="16"/>
-      <c r="P71" s="16"/>
-      <c r="Q71" s="16"/>
-      <c r="R71" s="16"/>
-      <c r="S71" s="16"/>
-    </row>
-    <row r="72" spans="2:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C72" s="24"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="12"/>
-      <c r="M72" s="12"/>
-      <c r="N72" s="12"/>
-      <c r="O72" s="12"/>
-      <c r="Q72" s="11"/>
-      <c r="R72" s="11"/>
-      <c r="S72" s="11"/>
-    </row>
-    <row r="73" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="25"/>
-      <c r="C73" s="26"/>
+    </row>
+    <row r="68" spans="2:17" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="44"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="39"/>
+      <c r="N68" s="39"/>
+      <c r="O68" s="22"/>
+      <c r="P68" s="22"/>
+      <c r="Q68" s="22"/>
+    </row>
+    <row r="69" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="44"/>
+      <c r="C69" s="44"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
+      <c r="H69" s="23"/>
+      <c r="I69" s="23"/>
+      <c r="J69" s="23"/>
+      <c r="K69" s="23"/>
+      <c r="L69" s="23"/>
+      <c r="M69" s="40"/>
+      <c r="N69" s="40"/>
+      <c r="O69" s="23"/>
+      <c r="P69" s="23"/>
+      <c r="Q69" s="23"/>
+    </row>
+    <row r="70" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="44"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
+      <c r="P70" s="22"/>
+      <c r="Q70" s="22"/>
+    </row>
+    <row r="71" spans="2:17" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
+      <c r="I71" s="23"/>
+      <c r="J71" s="23"/>
+      <c r="K71" s="23"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="23"/>
+      <c r="N71" s="23"/>
+      <c r="O71" s="23"/>
+      <c r="P71" s="23"/>
+      <c r="Q71" s="23"/>
+    </row>
+    <row r="72" spans="2:17" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="9"/>
+      <c r="N72" s="9"/>
+      <c r="O72" s="9"/>
+      <c r="Q72" s="8"/>
+    </row>
+    <row r="73" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="20"/>
+      <c r="C73" s="21"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -2441,14 +2285,12 @@
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
-      <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
-    </row>
-    <row r="74" spans="2:19" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74" s="24"/>
+    </row>
+    <row r="74" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="19"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -2459,14 +2301,12 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-      <c r="N74" s="12"/>
+      <c r="N74" s="9"/>
       <c r="Q74" s="1"/>
-      <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
-    </row>
-    <row r="75" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="25"/>
-      <c r="C75" s="26"/>
+    </row>
+    <row r="75" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="20"/>
+      <c r="C75" s="21"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -2479,16 +2319,14 @@
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
-      <c r="P75" s="11"/>
+      <c r="P75" s="8"/>
       <c r="Q75" s="1"/>
-      <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
-    </row>
-    <row r="76" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" s="24"/>
+    </row>
+    <row r="76" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="19"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
@@ -2500,15 +2338,13 @@
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
-      <c r="O76" s="12"/>
-      <c r="P76" s="11"/>
+      <c r="O76" s="9"/>
+      <c r="P76" s="8"/>
       <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-    </row>
-    <row r="77" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="25"/>
-      <c r="C77" s="26"/>
+    </row>
+    <row r="77" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="20"/>
+      <c r="C77" s="21"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -2523,14 +2359,12 @@
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-    </row>
-    <row r="78" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C78" s="24"/>
+    </row>
+    <row r="78" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" s="19"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
@@ -2543,14 +2377,12 @@
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
-      <c r="P78" s="12"/>
-      <c r="Q78" s="11"/>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-    </row>
-    <row r="79" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="25"/>
-      <c r="C79" s="26"/>
+      <c r="P78" s="9"/>
+      <c r="Q78" s="8"/>
+    </row>
+    <row r="79" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="20"/>
+      <c r="C79" s="21"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -2565,14 +2397,12 @@
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
-      <c r="R79" s="1"/>
-      <c r="S79" s="1"/>
-    </row>
-    <row r="80" spans="2:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C80" s="24"/>
+    </row>
+    <row r="80" spans="2:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C80" s="19"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -2585,14 +2415,12 @@
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
-      <c r="P80" s="12"/>
+      <c r="P80" s="9"/>
       <c r="Q80" s="1"/>
-      <c r="R80" s="1"/>
-      <c r="S80" s="1"/>
-    </row>
-    <row r="81" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="25"/>
-      <c r="C81" s="26"/>
+    </row>
+    <row r="81" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="20"/>
+      <c r="C81" s="21"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -2607,14 +2435,12 @@
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
-      <c r="R81" s="1"/>
-      <c r="S81" s="1"/>
-    </row>
-    <row r="82" spans="2:19" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C82" s="45"/>
+    </row>
+    <row r="82" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="50"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -2628,15 +2454,11 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
-      <c r="R82" s="1"/>
-      <c r="S82" s="1"/>
-    </row>
-    <row r="83" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="24"/>
+      <c r="Q82" s="9"/>
+    </row>
+    <row r="83" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="51"/>
+      <c r="C83" s="52"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -2649,189 +2471,77 @@
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
-      <c r="P83" s="12"/>
+      <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
-      <c r="R83" s="1"/>
-      <c r="S83" s="1"/>
-    </row>
-    <row r="84" spans="2:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="25"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
-      <c r="M84" s="1"/>
-      <c r="N84" s="1"/>
-      <c r="O84" s="1"/>
-      <c r="P84" s="1"/>
-      <c r="Q84" s="1"/>
-      <c r="R84" s="1"/>
-      <c r="S84" s="1"/>
-    </row>
-    <row r="85" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C85" s="24"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
-      <c r="L85" s="1"/>
-      <c r="M85" s="1"/>
-      <c r="N85" s="1"/>
-      <c r="O85" s="1"/>
-      <c r="P85" s="12"/>
-      <c r="Q85" s="1"/>
-      <c r="R85" s="1"/>
-      <c r="S85" s="1"/>
-    </row>
-    <row r="86" spans="2:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="25"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-      <c r="M86" s="1"/>
-      <c r="N86" s="1"/>
-      <c r="O86" s="1"/>
-      <c r="P86" s="1"/>
-      <c r="Q86" s="1"/>
-      <c r="R86" s="1"/>
-      <c r="S86" s="1"/>
-    </row>
-    <row r="87" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="24"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
-      <c r="M87" s="1"/>
-      <c r="N87" s="1"/>
-      <c r="O87" s="1"/>
-      <c r="P87" s="12"/>
-      <c r="Q87" s="1"/>
-      <c r="R87" s="1"/>
-      <c r="S87" s="11"/>
-    </row>
-    <row r="88" spans="2:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="25"/>
-      <c r="C88" s="26"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
-      <c r="N88" s="1"/>
-      <c r="O88" s="1"/>
-      <c r="P88" s="1"/>
-      <c r="Q88" s="1"/>
-      <c r="R88" s="1"/>
-      <c r="S88" s="1"/>
-    </row>
-    <row r="89" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" s="2"/>
-      <c r="Q89" s="2"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
-    </row>
-    <row r="90" spans="2:19" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="G90" s="34"/>
-      <c r="H90" s="42"/>
-      <c r="I90" s="42"/>
-      <c r="J90" s="44"/>
-      <c r="K90" s="44"/>
-      <c r="L90" s="44"/>
-      <c r="M90" s="7"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="2"/>
-      <c r="S90" s="2"/>
-    </row>
-    <row r="91" spans="2:19" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G91" s="34"/>
-      <c r="H91" s="43"/>
-      <c r="I91" s="43"/>
-      <c r="J91" s="44"/>
-      <c r="K91" s="44"/>
-      <c r="L91" s="44"/>
-      <c r="M91" s="7"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" s="2"/>
-      <c r="Q91" s="2"/>
-      <c r="R91" s="2"/>
-      <c r="S91" s="2"/>
+    </row>
+    <row r="84" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
+    </row>
+    <row r="85" spans="2:17" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G85" s="31"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="41"/>
+      <c r="J85" s="43"/>
+      <c r="K85" s="43"/>
+      <c r="L85" s="43"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+    </row>
+    <row r="86" spans="2:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G86" s="31"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="43"/>
+      <c r="K86" s="43"/>
+      <c r="L86" s="43"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="118">
+  <mergeCells count="111">
     <mergeCell ref="B10:C11"/>
     <mergeCell ref="B12:C13"/>
     <mergeCell ref="B14:C15"/>
     <mergeCell ref="B16:C17"/>
     <mergeCell ref="B18:C19"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="B2:S2"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B2:Q2"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="L3:O3"/>
@@ -2839,11 +2549,12 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C7"/>
     <mergeCell ref="B8:C9"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="N68:N69"/>
+    <mergeCell ref="O68:O69"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="J86:L86"/>
     <mergeCell ref="B68:C71"/>
     <mergeCell ref="M34:M35"/>
     <mergeCell ref="L34:L35"/>
@@ -2861,15 +2572,16 @@
     <mergeCell ref="B62:C63"/>
     <mergeCell ref="B64:C65"/>
     <mergeCell ref="B66:C67"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
     <mergeCell ref="Q68:Q69"/>
     <mergeCell ref="Q70:Q71"/>
     <mergeCell ref="L68:L69"/>
     <mergeCell ref="L70:L71"/>
     <mergeCell ref="M70:M71"/>
     <mergeCell ref="N70:N71"/>
-    <mergeCell ref="S22:S23"/>
     <mergeCell ref="F34:F35"/>
     <mergeCell ref="B22:C23"/>
     <mergeCell ref="D22:D23"/>
@@ -2879,18 +2591,13 @@
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="S34:S35"/>
     <mergeCell ref="Q34:Q35"/>
     <mergeCell ref="P34:P35"/>
     <mergeCell ref="O34:O35"/>
     <mergeCell ref="N34:N35"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="M68:M69"/>
     <mergeCell ref="B30:C31"/>
     <mergeCell ref="B32:C33"/>
-    <mergeCell ref="R34:R35"/>
     <mergeCell ref="B37:C38"/>
     <mergeCell ref="B46:C47"/>
     <mergeCell ref="K22:K23"/>
@@ -2898,17 +2605,10 @@
     <mergeCell ref="M22:M23"/>
     <mergeCell ref="N22:N23"/>
     <mergeCell ref="O22:O23"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F86:G86"/>
     <mergeCell ref="B78:C79"/>
     <mergeCell ref="B80:C81"/>
-    <mergeCell ref="B83:C84"/>
-    <mergeCell ref="B85:C86"/>
-    <mergeCell ref="B87:C88"/>
     <mergeCell ref="F68:F69"/>
     <mergeCell ref="G68:G69"/>
     <mergeCell ref="F70:F71"/>
@@ -2918,11 +2618,10 @@
     <mergeCell ref="B76:C77"/>
     <mergeCell ref="E68:E69"/>
     <mergeCell ref="E70:E71"/>
-    <mergeCell ref="B1:S1"/>
-    <mergeCell ref="R68:R69"/>
-    <mergeCell ref="R70:R71"/>
-    <mergeCell ref="S68:S69"/>
-    <mergeCell ref="S70:S71"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B82:C83"/>
+    <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B58:C59"/>
     <mergeCell ref="B60:C61"/>
@@ -2942,6 +2641,10 @@
     <mergeCell ref="P70:P71"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C41"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="B28:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="34" orientation="landscape" r:id="rId1"/>
